--- a/outputs/model_ecm/model_ecm_output.xlsx
+++ b/outputs/model_ecm/model_ecm_output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,630 @@
       <c r="T1" s="1" t="inlineStr">
         <is>
           <t>primary_chain_doc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>butter</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>observed</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>retail</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>prozorro</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.01931753309263347</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.1130442477150289</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-0.5842642909954745</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.007904731650635205</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>engle_granger_p=0.06; lags p=1 q=1</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Primary chain is strictly ProducerUA -&gt; ProZorro -&gt; Retail. Retail is estimated separately for silpo, novus, and silpo_novus. Combined rule: daily median of available silpo and novus standardized_type prices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>butter</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>retail</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>prozorro</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.01931753309263347</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-0.1130442477150289</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.5842642909954745</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.007904731650635205</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>engle_granger_p=0.06; lags p=1 q=1</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Primary chain is strictly ProducerUA -&gt; ProZorro -&gt; Retail. Retail is estimated separately for silpo, novus, and silpo_novus. Combined rule: daily median of available silpo and novus standardized_type prices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>silpo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>observed</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>producer_to_prozorro</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>prozorro</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>producer</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>197</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.002155003969288638</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.3006834081052232</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0.9538372381620318</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.295228800215539e-21</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>unreliable</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>engle_granger_p=1.912e-24; lags p=1 q=3</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Primary chain is strictly ProducerUA -&gt; ProZorro -&gt; Retail. Retail is estimated separately for silpo, novus, and silpo_novus. Combined rule: daily median of available silpo and novus standardized_type prices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>silpo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>observed</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>retail</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>prozorro</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>35</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.03780420860354025</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.07959450904544814</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.9002155090608189</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0004638981008127622</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>engle_granger_p=9.326e-06; lags p=1 q=0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Primary chain is strictly ProducerUA -&gt; ProZorro -&gt; Retail. Retail is estimated separately for silpo, novus, and silpo_novus. Combined rule: daily median of available silpo and novus standardized_type prices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>silpo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>producer_to_prozorro</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>prozorro</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>producer</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>197</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.002155003969288638</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.3006834081052232</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.9538372381620318</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.295228800215539e-21</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>unreliable</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>engle_granger_p=1.912e-24; lags p=1 q=3</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Primary chain is strictly ProducerUA -&gt; ProZorro -&gt; Retail. Retail is estimated separately for silpo, novus, and silpo_novus. Combined rule: daily median of available silpo and novus standardized_type prices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>silpo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>retail</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>prozorro</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>35</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.03780420860354025</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.07959450904544814</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.9002155090608189</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0004638981008127622</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>engle_granger_p=9.326e-06; lags p=1 q=0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Primary chain is strictly ProducerUA -&gt; ProZorro -&gt; Retail. Retail is estimated separately for silpo, novus, and silpo_novus. Combined rule: daily median of available silpo and novus standardized_type prices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>novus</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>observed</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>producer_to_prozorro</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>prozorro</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>producer</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>197</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.002155003969288638</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.3006834081052232</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.9538372381620318</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.295228800215539e-21</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>unreliable</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>engle_granger_p=1.912e-24; lags p=1 q=3</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Primary chain is strictly ProducerUA -&gt; ProZorro -&gt; Retail. Retail is estimated separately for silpo, novus, and silpo_novus. Combined rule: daily median of available silpo and novus standardized_type prices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>novus</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>producer_to_prozorro</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>prozorro</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>producer</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>197</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.002155003969288638</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.3006834081052232</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.9538372381620318</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.295228800215539e-21</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>unreliable</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>engle_granger_p=1.912e-24; lags p=1 q=3</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Primary chain is strictly ProducerUA -&gt; ProZorro -&gt; Retail. Retail is estimated separately for silpo, novus, and silpo_novus. Combined rule: daily median of available silpo and novus standardized_type prices.</t>
         </is>
       </c>
     </row>

--- a/outputs/model_ecm/model_ecm_output.xlsx
+++ b/outputs/model_ecm/model_ecm_output.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ECM_Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ECM_Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,733 +425,1233 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:AM8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>panel_level</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>panel_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>segment_name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>standardized_type</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>retailer</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>promo_variant</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>retailer_panel</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>price_variant</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>reconstruction_variant</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>farm_gate_source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>chain_direction</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>stage_from</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>stage_to</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>link</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>model_family</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>y_series</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>x_series</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>n_obs</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>sr_coef</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>lr_coef</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ect_coef</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ect_pvalue</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_short_p</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_long_p</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>vecm_rank</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>model_status</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>unreliable_flag</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>unreliable_reason</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>shock_dummy_included</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>promo_controls_included</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>ljungbox_p</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>arch_p</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>jb_p</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>primary_chain_doc</t>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>robust_linear_vs_pchip</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>interpolation_sensitive</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>robust_across_reconstruction</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>core_finding_flag</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>butter</t>
+          <t>product</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>silpo_novus</t>
+          <t>product::Сир твердий::Silpo::observed::initial::linear</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Сир твердий</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Сир твердий</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Silpo</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>observed</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>initial</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>prozorro_to_retail</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>reverse</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>FarmGateUA</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>retail_to_farmgateua</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>ECM</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>retail</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>prozorro</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>49</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-0.01931753309263347</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-0.1130442477150289</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-0.5842642909954745</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.007904731650635205</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>FarmGateUA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>36</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.0006243607074365656</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.05118671340979519</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-0.1304047954777818</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.01618224692205509</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>engle_granger_p=0.06; lags p=1 q=1</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Primary chain is strictly ProducerUA -&gt; ProZorro -&gt; Retail. Retail is estimated separately for silpo, novus, and silpo_novus. Combined rule: daily median of available silpo and novus standardized_type prices.</t>
-        </is>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.4546591156239976</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.1381724793310779</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.03583439982485814</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>engle_granger_p=0.02972; lags p=1 q=1</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>butter</t>
+          <t>average</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>silpo_novus</t>
+          <t>average::Silpo::observed::initial::linear</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>promo_controlled</t>
+          <t>all_products_average</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>all_products_average</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>all_products_average</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Silpo</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>observed</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>initial</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>prozorro_to_retail</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>forward</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>FarmGateUA</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>farmgateua_to_retail</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>ECM</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>retail</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>prozorro</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>49</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-0.01931753309263347</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-0.1130442477150289</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.5842642909954745</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.007904731650635205</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>FarmGateUA</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>45</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.9322772851319434</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-1.56271707030248</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-0.5172596333297379</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.278473445321985e-06</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>engle_granger_p=0.06; lags p=1 q=1</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Primary chain is strictly ProducerUA -&gt; ProZorro -&gt; Retail. Retail is estimated separately for silpo, novus, and silpo_novus. Combined rule: daily median of available silpo and novus standardized_type prices.</t>
-        </is>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.8972381078358652</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.7690540042589011</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.5837497917198777</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>engle_granger_p=0.002921; lags p=1 q=0</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>product::Молоко питне::Silpo::baseline::all_missing_filled::linear</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Молоко питне</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Молоко питне</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>milk</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>silpo</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>observed</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Silpo</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>all_missing_filled</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>producer_to_prozorro</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>forward</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>FarmGateUA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>farmgateua_to_retail</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>ECM</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>prozorro</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>producer</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>197</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-0.002155003969288638</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-0.3006834081052232</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-0.9538372381620318</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3.295228800215539e-21</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>unreliable</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>FarmGateUA</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>38</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.7299336643576522</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-1.463438024093577</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0.7973434884556778</v>
+      </c>
+      <c r="W4" t="n">
+        <v>9.528715655827255e-06</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.1144573872682583</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.3064661705975509</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.4681731907578257</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>engle_granger_p=0.00092; lags p=1 q=2</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
         <v>1</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>engle_granger_p=1.912e-24; lags p=1 q=3</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Primary chain is strictly ProducerUA -&gt; ProZorro -&gt; Retail. Retail is estimated separately for silpo, novus, and silpo_novus. Combined rule: daily median of available silpo and novus standardized_type prices.</t>
-        </is>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>milk</t>
+          <t>average</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>silpo</t>
+          <t>average::Silpo::observed::all_missing_filled::linear</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>all_products_average</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>all_products_average</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>all_products_average</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Silpo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>observed</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>all_missing_filled</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>prozorro_to_retail</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>forward</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>FarmGateUA</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>farmgateua_to_retail</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>ECM</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>retail</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>prozorro</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>35</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.03780420860354025</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.07959450904544814</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-0.9002155090608189</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.0004638981008127622</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>FarmGateUA</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>45</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.4518884015846381</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-1.469903753919038</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.6977591555383247</v>
+      </c>
+      <c r="W5" t="n">
+        <v>5.092795057104528e-07</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>engle_granger_p=9.326e-06; lags p=1 q=0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Primary chain is strictly ProducerUA -&gt; ProZorro -&gt; Retail. Retail is estimated separately for silpo, novus, and silpo_novus. Combined rule: daily median of available silpo and novus standardized_type prices.</t>
-        </is>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.7970888264642652</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.7870655941841516</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.6313790892338038</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>engle_granger_p=0.000208; lags p=1 q=0</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>milk</t>
+          <t>average</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>silpo</t>
+          <t>average::Silpo::observed::initial::pchip</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>promo_controlled</t>
+          <t>all_products_average</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>all_products_average</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>all_products_average</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Silpo</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>observed</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>pchip</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>initial</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>producer_to_prozorro</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>forward</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>FarmGateUA</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>farmgateua_to_retail</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>ECM</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>prozorro</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>producer</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>197</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-0.002155003969288638</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-0.3006834081052232</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-0.9538372381620318</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3.295228800215539e-21</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>unreliable</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>FarmGateUA</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>45</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.7725216333196893</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-1.449885237251225</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.516964061678618</v>
+      </c>
+      <c r="W6" t="n">
+        <v>4.607319487298131e-06</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.8977475095145333</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.8019656365888165</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.5416586765569108</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>engle_granger_p=0.002787; lags p=1 q=0</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>engle_granger_p=1.912e-24; lags p=1 q=3</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Primary chain is strictly ProducerUA -&gt; ProZorro -&gt; Retail. Retail is estimated separately for silpo, novus, and silpo_novus. Combined rule: daily median of available silpo and novus standardized_type prices.</t>
-        </is>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>product::Молоко питне::Silpo::baseline::all_missing_filled::pchip</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Молоко питне</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Молоко питне</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>milk</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>silpo</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>promo_controlled</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Silpo</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>pchip</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>all_missing_filled</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>prozorro_to_retail</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>forward</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>FarmGateUA</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>farmgateua_to_retail</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>ECM</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>retail</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>prozorro</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>35</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.03780420860354025</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.07959450904544814</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-0.9002155090608189</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.0004638981008127622</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>FarmGateUA</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>39</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.3184687744149954</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-1.376078842060526</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-0.7710056136386508</v>
+      </c>
+      <c r="W7" t="n">
+        <v>9.153908723126643e-05</v>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>engle_granger_p=9.326e-06; lags p=1 q=0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Primary chain is strictly ProducerUA -&gt; ProZorro -&gt; Retail. Retail is estimated separately for silpo, novus, and silpo_novus. Combined rule: daily median of available silpo and novus standardized_type prices.</t>
-        </is>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.2986309004515825</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.7193751009761611</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.3295111856425572</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>engle_granger_p=9.881e-05; lags p=1 q=0</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>milk</t>
+          <t>average</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>novus</t>
+          <t>average::Silpo::observed::all_missing_filled::pchip</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>all_products_average</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>all_products_average</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>all_products_average</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Silpo</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>observed</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>pchip</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>all_missing_filled</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>producer_to_prozorro</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>forward</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>FarmGateUA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>farmgateua_to_retail</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>ECM</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>prozorro</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>producer</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>197</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-0.002155003969288638</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-0.3006834081052232</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-0.9538372381620318</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3.295228800215539e-21</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>unreliable</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>FarmGateUA</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>45</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.4031624181582367</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-1.450887424487711</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-0.7128005383669054</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.106198918845673e-07</v>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.801596868197212</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.7694835593364274</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.598681891822242</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>engle_granger_p=0.0001423; lags p=1 q=0</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>engle_granger_p=1.912e-24; lags p=1 q=3</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Primary chain is strictly ProducerUA -&gt; ProZorro -&gt; Retail. Retail is estimated separately for silpo, novus, and silpo_novus. Combined rule: daily median of available silpo and novus standardized_type prices.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>milk</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>novus</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>promo_controlled</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>producer_to_prozorro</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ECM</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>prozorro</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>producer</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>197</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-0.002155003969288638</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-0.3006834081052232</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-0.9538372381620318</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3.295228800215539e-21</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>unreliable</t>
-        </is>
-      </c>
-      <c r="R9" t="n">
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
         <v>1</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>engle_granger_p=1.912e-24; lags p=1 q=3</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Primary chain is strictly ProducerUA -&gt; ProZorro -&gt; Retail. Retail is estimated separately for silpo, novus, and silpo_novus. Combined rule: daily median of available silpo and novus standardized_type prices.</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
